--- a/eval_output/BASE_CIFAR_noniid1.xlsx
+++ b/eval_output/BASE_CIFAR_noniid1.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102465243932.4201</v>
+        <v>102570309443.5909</v>
       </c>
       <c r="D2" t="n">
         <v>528795200</v>
@@ -503,7 +503,7 @@
         <v>2121559808</v>
       </c>
       <c r="F2" t="n">
-        <v>62.2445999749883</v>
+        <v>62.3084241602731</v>
       </c>
       <c r="G2" t="n">
         <v>476754112</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102485576945.1084</v>
+        <v>102588473199.4727</v>
       </c>
       <c r="D3" t="n">
         <v>528418784</v>
@@ -536,7 +536,7 @@
         <v>2119354624</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>62.25695167779504</v>
+        <v>62.31945810383795</v>
       </c>
       <c r="G3" t="n">
         <v>476754112</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>102388254705.2133</v>
+        <v>102410431990.7889</v>
       </c>
       <c r="D4" t="n">
         <v>502500096</v>
@@ -569,7 +569,7 @@
         <v>2120562176</v>
       </c>
       <c r="F4" t="n">
-        <v>62.19783130040214</v>
+        <v>62.21130334434804</v>
       </c>
       <c r="G4" t="n">
         <v>476754112</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>103133937490.9694</v>
+        <v>103301116167.6879</v>
       </c>
       <c r="D6" t="n">
         <v>476754112</v>
@@ -635,7 +635,7 @@
         <v>2121454848</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>62.65081150057846</v>
+        <v>62.75236759372117</v>
       </c>
       <c r="G6" t="n">
         <v>476754112</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>103280750180.8148</v>
+        <v>103409673246.8193</v>
       </c>
       <c r="D8" t="n">
         <v>528983456</v>
@@ -701,7 +701,7 @@
         <v>2119354624</v>
       </c>
       <c r="F8" t="n">
-        <v>62.73999586007413</v>
+        <v>62.81831280309815</v>
       </c>
       <c r="G8" t="n">
         <v>476754112</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103302811838.3677</v>
+        <v>103350244739.6297</v>
       </c>
       <c r="D9" t="n">
         <v>528795200</v>
@@ -734,7 +734,7 @@
         <v>2120562176</v>
       </c>
       <c r="F9" t="n">
-        <v>62.75339766342188</v>
+        <v>62.78221174565498</v>
       </c>
       <c r="G9" t="n">
         <v>476754112</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>104892474235.4872</v>
+        <v>104920886764.7325</v>
       </c>
       <c r="D10" t="n">
         <v>502633472</v>
@@ -767,7 +767,7 @@
         <v>2122452352</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>63.71907047311379</v>
+        <v>63.73633024285891</v>
       </c>
       <c r="G10" t="n">
         <v>476754112</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103866166022.2881</v>
+        <v>103871917623.683</v>
       </c>
       <c r="D12" t="n">
         <v>476963552</v>
@@ -833,7 +833,7 @@
         <v>2122924928</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>63.09561863979008</v>
+        <v>63.09911256723617</v>
       </c>
       <c r="G12" t="n">
         <v>476754112</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66556819490.17648</v>
+        <v>66641090602.05859</v>
       </c>
       <c r="D2" t="n">
         <v>528654048</v>
@@ -960,7 +960,7 @@
         <v>1594476672</v>
       </c>
       <c r="F2" t="n">
-        <v>59.42734980949667</v>
+        <v>59.50259392246684</v>
       </c>
       <c r="G2" t="n">
         <v>476712224</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66673872249.52612</v>
+        <v>66760721406.09438</v>
       </c>
       <c r="D3" t="n">
         <v>528418784</v>
@@ -993,7 +993,7 @@
         <v>1594581760</v>
       </c>
       <c r="F3" t="n">
-        <v>59.53186404754653</v>
+        <v>59.60941004880645</v>
       </c>
       <c r="G3" t="n">
         <v>476712224</v>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67004444638.24005</v>
+        <v>67206505617.21637</v>
       </c>
       <c r="D4" t="n">
         <v>502500096</v>
@@ -1026,7 +1026,7 @@
         <v>1594319104</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.82702600287949</v>
+        <v>60.00744250373479</v>
       </c>
       <c r="G4" t="n">
         <v>476712224</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66823412365.73344</v>
+        <v>67004481458.58715</v>
       </c>
       <c r="D5" t="n">
         <v>476712224</v>
@@ -1059,7 +1059,7 @@
         <v>1592481536</v>
       </c>
       <c r="F5" t="n">
-        <v>59.66538564404826</v>
+        <v>59.82705887908457</v>
       </c>
       <c r="G5" t="n">
         <v>476712224</v>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67301586009.96528</v>
+        <v>67417338901.57124</v>
       </c>
       <c r="D6" t="n">
         <v>476712224</v>
@@ -1092,7 +1092,7 @@
         <v>1594424320</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>60.09233802313003</v>
+        <v>60.19569163337793</v>
       </c>
       <c r="G6" t="n">
         <v>476712224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67367143919.52001</v>
+        <v>67439863777.81719</v>
       </c>
       <c r="D8" t="n">
         <v>528795232</v>
@@ -1158,7 +1158,7 @@
         <v>1595841920</v>
       </c>
       <c r="F8" t="n">
-        <v>60.15087346478321</v>
+        <v>60.21580367764835</v>
       </c>
       <c r="G8" t="n">
         <v>476712224</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67296291825.89382</v>
+        <v>67379630520.86582</v>
       </c>
       <c r="D9" t="n">
         <v>528654048</v>
@@ -1191,7 +1191,7 @@
         <v>1596681728</v>
       </c>
       <c r="F9" t="n">
-        <v>60.08761094435462</v>
+        <v>60.16202251955766</v>
       </c>
       <c r="G9" t="n">
         <v>476712224</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68290359273.76432</v>
+        <v>68406970153.51218</v>
       </c>
       <c r="D10" t="n">
         <v>502589024</v>
@@ -1224,7 +1224,7 @@
         <v>1596419200</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>60.9751953333225</v>
+        <v>61.0793150252707</v>
       </c>
       <c r="G10" t="n">
         <v>476712224</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67332147241.47946</v>
+        <v>67564763564.42191</v>
       </c>
       <c r="D11" t="n">
         <v>476754112</v>
@@ -1257,7 +1257,7 @@
         <v>1591536512</v>
       </c>
       <c r="F11" t="n">
-        <v>60.11962557998317</v>
+        <v>60.32732438080913</v>
       </c>
       <c r="G11" t="n">
         <v>476712224</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67684841613.3098</v>
+        <v>67728809760.56606</v>
       </c>
       <c r="D12" t="n">
         <v>476879744</v>
@@ -1290,7 +1290,7 @@
         <v>1595369216</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>60.43453984378292</v>
+        <v>60.47379818706748</v>
       </c>
       <c r="G12" t="n">
         <v>476712224</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30475435726.28786</v>
+        <v>30620888851.83229</v>
       </c>
       <c r="D2" t="n">
         <v>528512864</v>
@@ -1417,7 +1417,7 @@
         <v>1072433856</v>
       </c>
       <c r="F2" t="n">
-        <v>50.95598468804143</v>
+        <v>51.19918735476086</v>
       </c>
       <c r="G2" t="n">
         <v>476670336</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30405072052.84133</v>
+        <v>30470465756.98712</v>
       </c>
       <c r="D3" t="n">
         <v>528418784</v>
@@ -1450,7 +1450,7 @@
         <v>1072013888</v>
       </c>
       <c r="F3" t="n">
-        <v>50.83833418752233</v>
+        <v>50.94767472713183</v>
       </c>
       <c r="G3" t="n">
         <v>476670336</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30851778198.39835</v>
+        <v>31038544827.74292</v>
       </c>
       <c r="D4" t="n">
         <v>502500096</v>
@@ -1483,7 +1483,7 @@
         <v>1074744064</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>51.5852423438977</v>
+        <v>51.89752262072765</v>
       </c>
       <c r="G4" t="n">
         <v>476670336</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30421815538.75256</v>
+        <v>30689746626.00729</v>
       </c>
       <c r="D5" t="n">
         <v>476670336</v>
@@ -1516,7 +1516,7 @@
         <v>1073431424</v>
       </c>
       <c r="F5" t="n">
-        <v>50.86632987622649</v>
+        <v>51.31431993950967</v>
       </c>
       <c r="G5" t="n">
         <v>476670336</v>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30891656633.83216</v>
+        <v>31051498601.87585</v>
       </c>
       <c r="D6" t="n">
         <v>476670336</v>
@@ -1549,7 +1549,7 @@
         <v>1072433856</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>51.65192046996614</v>
+        <v>51.91918178000263</v>
       </c>
       <c r="G6" t="n">
         <v>476670336</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30899564333.42302</v>
+        <v>30983012084.62643</v>
       </c>
       <c r="D8" t="n">
         <v>528606976</v>
@@ -1615,7 +1615,7 @@
         <v>1074376448</v>
       </c>
       <c r="F8" t="n">
-        <v>51.6651424177305</v>
+        <v>51.80466994969963</v>
       </c>
       <c r="G8" t="n">
         <v>476670336</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30865607708.51523</v>
+        <v>30930810452.2156</v>
       </c>
       <c r="D9" t="n">
         <v>528512864</v>
@@ -1648,7 +1648,7 @@
         <v>1073956480</v>
       </c>
       <c r="F9" t="n">
-        <v>51.60836576408725</v>
+        <v>51.71738701121411</v>
       </c>
       <c r="G9" t="n">
         <v>476670336</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31340504381.43564</v>
+        <v>31561700648.53667</v>
       </c>
       <c r="D10" t="n">
         <v>502544544</v>
@@ -1681,7 +1681,7 @@
         <v>1074481536</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>52.40240945918233</v>
+        <v>52.77225728353122</v>
       </c>
       <c r="G10" t="n">
         <v>476670336</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30897445587.7033</v>
+        <v>31185019764.61638</v>
       </c>
       <c r="D11" t="n">
         <v>476712256</v>
@@ -1714,7 +1714,7 @@
         <v>1073851392</v>
       </c>
       <c r="F11" t="n">
-        <v>51.66159980146011</v>
+        <v>52.14243379140101</v>
       </c>
       <c r="G11" t="n">
         <v>476670336</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31132411279.25196</v>
+        <v>31293464575.31327</v>
       </c>
       <c r="D12" t="n">
         <v>476754112</v>
@@ -1747,7 +1747,7 @@
         <v>1073168960</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>52.05447058067723</v>
+        <v>52.32375727313885</v>
       </c>
       <c r="G12" t="n">
         <v>476670336</v>
